--- a/ZonasEscolares/excels/AREQUIPA-AREQUIPA-CAYMA.xlsx
+++ b/ZonasEscolares/excels/AREQUIPA-AREQUIPA-CAYMA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/AREQUIPA-AREQUIPA-CAYMA.xlsx
+++ b/ZonasEscolares/excels/AREQUIPA-AREQUIPA-CAYMA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>40040 JOSE TRINIDAD MORAN</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-16.34449</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-71.54299</v>
-      </c>
-      <c r="I2" t="n">
-        <v>453</v>
-      </c>
-      <c r="J2" t="n">
-        <v>31</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-16.34449</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-71.54299</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>40046 JOSE L. CORNEJO A.</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-16.36185</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-71.54219999999999</v>
-      </c>
-      <c r="I3" t="n">
-        <v>547</v>
-      </c>
-      <c r="J3" t="n">
-        <v>37</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-16.36185</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-71.5422</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>547</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>40049 CORONEL FRANCISCO BOLOGNESI CERVANTES</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-16.35085</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-71.54295</v>
-      </c>
-      <c r="I4" t="n">
-        <v>896</v>
-      </c>
-      <c r="J4" t="n">
-        <v>47</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-16.35085</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-71.54295</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>40052 EL PERUANO DEL MILENIO ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-16.35301</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-71.55</v>
-      </c>
-      <c r="I5" t="n">
-        <v>635</v>
-      </c>
-      <c r="J5" t="n">
-        <v>42</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-16.35301</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-71.55</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>40606 SEUL</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-16.34906</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-71.54868</v>
-      </c>
-      <c r="I6" t="n">
-        <v>260</v>
-      </c>
-      <c r="J6" t="n">
-        <v>14</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-16.34906</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-71.54868</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>40618 MONSEÑOR JOSE DE PIRO D' AMICO INGUANEZ / 40618 MONSEÑOR JOSE DE PIRO D'AMICO INGUANEZ</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-16.362225</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-71.5453</v>
-      </c>
-      <c r="I7" t="n">
-        <v>286</v>
-      </c>
-      <c r="J7" t="n">
-        <v>15</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-16.362225</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-71.5453</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>40654</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-16.33843</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-71.54356</v>
-      </c>
-      <c r="I8" t="n">
-        <v>268</v>
-      </c>
-      <c r="J8" t="n">
-        <v>14</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-16.33843</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-71.54356</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>40669 DEAN VALDIVIA</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-16.32934</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-71.54485099999999</v>
-      </c>
-      <c r="I9" t="n">
-        <v>606</v>
-      </c>
-      <c r="J9" t="n">
-        <v>26</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-16.32934</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-71.544851</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>HONORIO DELGADO ESPINOZA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-16.3874</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-71.5489</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1203</v>
-      </c>
-      <c r="J10" t="n">
-        <v>68</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-16.3874</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-71.5489</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1203</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>EL PIONERO G-2</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-16.3364</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-71.5532</v>
-      </c>
-      <c r="I11" t="n">
-        <v>372</v>
-      </c>
-      <c r="J11" t="n">
-        <v>19</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-16.3364</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-71.5532</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>LEON XIII</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-16.34986</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-71.54288</v>
-      </c>
-      <c r="I12" t="n">
-        <v>909</v>
-      </c>
-      <c r="J12" t="n">
-        <v>58</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-16.34986</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-71.54288</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>909</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>SAN JOSE DE CALASANZ</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-16.33053</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-71.54596600000001</v>
-      </c>
-      <c r="I13" t="n">
-        <v>413</v>
-      </c>
-      <c r="J13" t="n">
-        <v>17</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-16.33053</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-71.545966</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>FLORA TRISTAN</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-16.391</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-71.54756</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-16.391</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-71.54756</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>NIÑO JESUS EL TERREMOTITO</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-16.355156</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-71.542939</v>
-      </c>
-      <c r="I15" t="n">
-        <v>363</v>
-      </c>
-      <c r="J15" t="n">
-        <v>22</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-16.355156</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-71.542939</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>JAMES CLERK MAXWELL</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-16.3659</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-71.54599</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1126</v>
-      </c>
-      <c r="J16" t="n">
-        <v>52</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-16.3659</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-71.54599</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1126</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>MARIA MAZZARELLO</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-16.33065</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-71.5448</v>
-      </c>
-      <c r="I17" t="n">
-        <v>344</v>
-      </c>
-      <c r="J17" t="n">
-        <v>18</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-16.33065</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-71.5448</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>CRISTO REY</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-16.3259</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-71.5487</v>
-      </c>
-      <c r="I18" t="n">
-        <v>630</v>
-      </c>
-      <c r="J18" t="n">
-        <v>27</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-16.3259</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-71.5487</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>EL NAZARENO</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-16.326817</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-71.549977</v>
-      </c>
-      <c r="I19" t="n">
-        <v>351</v>
-      </c>
-      <c r="J19" t="n">
-        <v>17</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-16.326817</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-71.549977</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>JOHN G. LAKE</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-16.33252</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-71.54935999999999</v>
-      </c>
-      <c r="I20" t="n">
-        <v>485</v>
-      </c>
-      <c r="J20" t="n">
-        <v>17</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-16.33252</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-71.54936</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>485</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>MI PEQUEÑO ESPACIO</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-16.3918</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-71.54783999999999</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-16.3918</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-71.54784</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>JESUS EL MESIAS</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-16.34996</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-71.54897</v>
-      </c>
-      <c r="I22" t="n">
-        <v>3</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-16.34996</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-71.54897</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>EL MERCEDARIO RVDO PADRE ELEUTERIO ALARCON BEJARANO</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-16.34483</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-71.54367999999999</v>
-      </c>
-      <c r="I23" t="n">
-        <v>468</v>
-      </c>
-      <c r="J23" t="n">
-        <v>31</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-16.34483</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-71.54368</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>40616 CASIMIRO CUADROS I</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-16.34831</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-71.55226999999999</v>
-      </c>
-      <c r="I24" t="n">
-        <v>884</v>
-      </c>
-      <c r="J24" t="n">
-        <v>45</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-16.34831</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-71.55227</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>884</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>SAN JUAN MASIAS</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-16.331039</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-71.549037</v>
-      </c>
-      <c r="I25" t="n">
-        <v>290</v>
-      </c>
-      <c r="J25" t="n">
-        <v>18</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-16.331039</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-71.549037</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>MI DIVINO NIÑO JESUS</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-16.33772</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-71.55009</v>
-      </c>
-      <c r="I26" t="n">
-        <v>206</v>
-      </c>
-      <c r="J26" t="n">
-        <v>10</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-16.33772</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-71.55009</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>REY DE REYES</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-16.386375</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-71.54989999999999</v>
-      </c>
-      <c r="I27" t="n">
-        <v>324</v>
-      </c>
-      <c r="J27" t="n">
-        <v>19</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-16.386375</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-71.5499</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>REY DE REYES</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-16.38469</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-71.55029999999999</v>
-      </c>
-      <c r="I28" t="n">
-        <v>205</v>
-      </c>
-      <c r="J28" t="n">
-        <v>26</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-16.38469</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-71.5503</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>THOMAS M.C. II</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-16.345349</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-71.544853</v>
-      </c>
-      <c r="I29" t="n">
-        <v>224</v>
-      </c>
-      <c r="J29" t="n">
-        <v>16</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-16.345349</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-71.544853</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>BALMER CAYMA</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-16.3591</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-71.54300000000001</v>
-      </c>
-      <c r="I30" t="n">
-        <v>291</v>
-      </c>
-      <c r="J30" t="n">
-        <v>16</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-16.3591</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-71.543</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>JOULE CAYMA</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-16.3593</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-71.5414</v>
-      </c>
-      <c r="I31" t="n">
-        <v>239</v>
-      </c>
-      <c r="J31" t="n">
-        <v>17</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-16.3593</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-71.5414</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-16.38125</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-71.539879</v>
-      </c>
-      <c r="I32" t="n">
-        <v>782</v>
-      </c>
-      <c r="J32" t="n">
-        <v>64</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-16.38125</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-71.539879</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>782</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>NIÑO MAGISTRAL</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-16.35972</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-71.54306</v>
-      </c>
-      <c r="I33" t="n">
-        <v>297</v>
-      </c>
-      <c r="J33" t="n">
-        <v>11</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-16.35972</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-71.54306</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/AREQUIPA-AREQUIPA-CAYMA.xlsx
+++ b/ZonasEscolares/excels/AREQUIPA-AREQUIPA-CAYMA.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>58623</t>
+          <t>59118</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>40040 JOSE TRINIDAD MORAN</t>
+          <t>FLORA TRISTAN</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-16.34449</t>
+          <t>-16.391</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-71.54299</t>
+          <t>-71.54756</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58642</t>
+          <t>277673</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>40046 JOSE L. CORNEJO A.</t>
+          <t>MI PEQUEÑO ESPACIO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-16.36185</t>
+          <t>-16.3918</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-71.5422</t>
+          <t>-71.54784</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>58656</t>
+          <t>532273</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>40049 CORONEL FRANCISCO BOLOGNESI CERVANTES</t>
+          <t>JESUS EL MESIAS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-16.35085</t>
+          <t>-16.34996</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-71.54295</t>
+          <t>-71.54897</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58699</t>
+          <t>642870</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>40052 EL PERUANO DEL MILENIO ALMIRANTE MIGUEL GRAU</t>
+          <t>MI DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-16.35301</t>
+          <t>-16.33772</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-71.55</t>
+          <t>-71.55009</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>206</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,37 +749,37 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>58717</t>
+          <t>908209</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>40606 SEUL</t>
+          <t>NIÑO MAGISTRAL</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-16.34906</t>
+          <t>-16.35972</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-71.54868</t>
+          <t>-71.54306</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>297</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -811,37 +811,37 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58741</t>
+          <t>58717</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>40618 MONSEÑOR JOSE DE PIRO D' AMICO INGUANEZ / 40618 MONSEÑOR JOSE DE PIRO D'AMICO INGUANEZ</t>
+          <t>40606 SEUL</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-16.362225</t>
+          <t>-16.34906</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-71.5453</t>
+          <t>-71.54868</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>260</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>58760</t>
+          <t>58741</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>40669 DEAN VALDIVIA</t>
+          <t>40618 MONSEÑOR JOSE DE PIRO D' AMICO INGUANEZ / 40618 MONSEÑOR JOSE DE PIRO D'AMICO INGUANEZ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-16.32934</t>
+          <t>-16.362225</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-71.544851</t>
+          <t>-71.5453</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>286</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>58859</t>
+          <t>785048</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>HONORIO DELGADO ESPINOZA</t>
+          <t>THOMAS M.C. II</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-16.3874</t>
+          <t>-16.345349</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-71.5489</t>
+          <t>-71.544853</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>224</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>58963</t>
+          <t>824889</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>EL PIONERO G-2</t>
+          <t>BALMER CAYMA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-16.3364</t>
+          <t>-16.3591</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-71.5532</t>
+          <t>-71.543</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>291</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>58977</t>
+          <t>59019</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>LEON XIII</t>
+          <t>SAN JOSE DE CALASANZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-16.34986</t>
+          <t>-16.33053</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-71.54288</t>
+          <t>-71.545966</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>413</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,27 +1183,27 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>59019</t>
+          <t>59811</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SAN JOSE DE CALASANZ</t>
+          <t>EL NAZARENO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-16.33053</t>
+          <t>-16.326817</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-71.545966</t>
+          <t>-71.549977</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>351</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1245,37 +1245,37 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>59118</t>
+          <t>113455</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FLORA TRISTAN</t>
+          <t>JOHN G. LAKE</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-16.391</t>
+          <t>-16.33252</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-71.54756</t>
+          <t>-71.54936</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>485</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>59175</t>
+          <t>825959</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>NIÑO JESUS EL TERREMOTITO</t>
+          <t>JOULE CAYMA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-16.355156</t>
+          <t>-16.3593</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-71.542939</t>
+          <t>-71.5414</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>239</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>59284</t>
+          <t>59298</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JAMES CLERK MAXWELL</t>
+          <t>MARIA MAZZARELLO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-16.3659</t>
+          <t>-16.33065</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-71.54599</t>
+          <t>-71.5448</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1126</t>
+          <t>344</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,27 +1431,27 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>59298</t>
+          <t>547873</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MARIA MAZZARELLO</t>
+          <t>SAN JUAN MASIAS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-16.33065</t>
+          <t>-16.331039</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-71.5448</t>
+          <t>-71.549037</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>290</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>59806</t>
+          <t>58963</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CRISTO REY</t>
+          <t>EL PIONERO G-2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-16.3259</t>
+          <t>-16.3364</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-71.5487</t>
+          <t>-71.5532</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>372</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>59811</t>
+          <t>747754</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>EL NAZARENO</t>
+          <t>REY DE REYES</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-16.326817</t>
+          <t>-16.386375</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-71.549977</t>
+          <t>-71.5499</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>324</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>113455</t>
+          <t>59175</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JOHN G. LAKE</t>
+          <t>NIÑO JESUS EL TERREMOTITO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-16.33252</t>
+          <t>-16.355156</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-71.54936</t>
+          <t>-71.542939</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>363</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,37 +1679,37 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>277673</t>
+          <t>58760</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MI PEQUEÑO ESPACIO</t>
+          <t>40669 DEAN VALDIVIA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-16.3918</t>
+          <t>-16.32934</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-71.54784</t>
+          <t>-71.544851</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>606</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1741,37 +1741,37 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>532273</t>
+          <t>779636</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>JESUS EL MESIAS</t>
+          <t>REY DE REYES</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-16.34996</t>
+          <t>-16.38469</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-71.54897</t>
+          <t>-71.5503</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>205</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>546345</t>
+          <t>59806</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>EL MERCEDARIO RVDO PADRE ELEUTERIO ALARCON BEJARANO</t>
+          <t>CRISTO REY</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-16.34483</t>
+          <t>-16.3259</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-71.54368</t>
+          <t>-71.5487</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>630</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>547613</t>
+          <t>58623</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>40616 CASIMIRO CUADROS I</t>
+          <t>40040 JOSE TRINIDAD MORAN</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-16.34831</t>
+          <t>-16.34449</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-71.55227</t>
+          <t>-71.54299</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>453</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>547873</t>
+          <t>546345</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SAN JUAN MASIAS</t>
+          <t>EL MERCEDARIO RVDO PADRE ELEUTERIO ALARCON BEJARANO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-16.331039</t>
+          <t>-16.34483</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-71.549037</t>
+          <t>-71.54368</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>468</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>642870</t>
+          <t>58642</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MI DIVINO NIÑO JESUS</t>
+          <t>40046 JOSE L. CORNEJO A.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-16.33772</t>
+          <t>-16.36185</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-71.55009</t>
+          <t>-71.5422</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>547</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>747754</t>
+          <t>58699</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>REY DE REYES</t>
+          <t>40052 EL PERUANO DEL MILENIO ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-16.386375</t>
+          <t>-16.35301</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-71.5499</t>
+          <t>-71.55</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>635</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>779636</t>
+          <t>547613</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>REY DE REYES</t>
+          <t>40616 CASIMIRO CUADROS I</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-16.38469</t>
+          <t>-16.34831</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-71.5503</t>
+          <t>-71.55227</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>884</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>785048</t>
+          <t>58656</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>THOMAS M.C. II</t>
+          <t>40049 CORONEL FRANCISCO BOLOGNESI CERVANTES</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-16.345349</t>
+          <t>-16.35085</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-71.544853</t>
+          <t>-71.54295</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>896</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>824889</t>
+          <t>59284</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>BALMER CAYMA</t>
+          <t>JAMES CLERK MAXWELL</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-16.3591</t>
+          <t>-16.3659</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-71.543</t>
+          <t>-71.54599</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>1126</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>825959</t>
+          <t>58977</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>JOULE CAYMA</t>
+          <t>LEON XIII</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-16.3593</t>
+          <t>-16.34986</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-71.5414</t>
+          <t>-71.54288</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>909</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>908209</t>
+          <t>58859</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NIÑO MAGISTRAL</t>
+          <t>HONORIO DELGADO ESPINOZA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-16.35972</t>
+          <t>-16.3874</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-71.54306</t>
+          <t>-71.5489</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>1203</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>68</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">

--- a/ZonasEscolares/excels/AREQUIPA-AREQUIPA-CAYMA.xlsx
+++ b/ZonasEscolares/excels/AREQUIPA-AREQUIPA-CAYMA.xlsx
@@ -759,12 +759,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-16.35972</t>
+          <t>-16.35029076</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-71.54306</t>
+          <t>-71.5408911</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">

--- a/ZonasEscolares/excels/AREQUIPA-AREQUIPA-CAYMA.xlsx
+++ b/ZonasEscolares/excels/AREQUIPA-AREQUIPA-CAYMA.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>59118</t>
+          <t>908209</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FLORA TRISTAN</t>
+          <t>NIÑO MAGISTRAL</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-16.391</t>
+          <t>297</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-71.54756</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-16.35029076</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-71.5408911</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>277673</t>
+          <t>851298</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MI PEQUEÑO ESPACIO</t>
+          <t>SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-16.3918</t>
+          <t>782</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-71.54784</t>
+          <t>64</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-16.38125</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-71.539879</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>532273</t>
+          <t>825959</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>JESUS EL MESIAS</t>
+          <t>JOULE CAYMA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-16.34996</t>
+          <t>239</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-71.54897</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-16.3593</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-71.5414</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>642870</t>
+          <t>824889</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MI DIVINO NIÑO JESUS</t>
+          <t>BALMER CAYMA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-16.33772</t>
+          <t>291</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-71.55009</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>-16.3591</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-71.543</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>908209</t>
+          <t>785048</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NIÑO MAGISTRAL</t>
+          <t>THOMAS M.C. II</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-16.35029076</t>
+          <t>224</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-71.5408911</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>-16.345349</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-71.544853</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,37 +811,37 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58717</t>
+          <t>779636</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>40606 SEUL</t>
+          <t>REY DE REYES</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-16.34906</t>
+          <t>205</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-71.54868</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>-16.38469</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-71.5503</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>58755</t>
+          <t>747754</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>40654</t>
+          <t>REY DE REYES</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-16.33843</t>
+          <t>324</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-71.54356</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>-16.386375</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-71.5499</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>58741</t>
+          <t>642870</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>40618 MONSEÑOR JOSE DE PIRO D' AMICO INGUANEZ / 40618 MONSEÑOR JOSE DE PIRO D'AMICO INGUANEZ</t>
+          <t>MI DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-16.362225</t>
+          <t>206</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-71.5453</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>-16.33772</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-71.55009</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>785048</t>
+          <t>547873</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>THOMAS M.C. II</t>
+          <t>SAN JUAN MASIAS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-16.345349</t>
+          <t>290</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-71.544853</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>-16.331039</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-71.549037</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>824889</t>
+          <t>547613</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BALMER CAYMA</t>
+          <t>40616 CASIMIRO CUADROS I</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-16.3591</t>
+          <t>884</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-71.543</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>-16.34831</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-71.55227</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>59019</t>
+          <t>546345</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SAN JOSE DE CALASANZ</t>
+          <t>EL MERCEDARIO RVDO PADRE ELEUTERIO ALARCON BEJARANO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-16.33053</t>
+          <t>468</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-71.545966</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>-16.34483</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-71.54368</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,37 +1183,37 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>59811</t>
+          <t>532273</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>EL NAZARENO</t>
+          <t>JESUS EL MESIAS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-16.326817</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-71.549977</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>-16.34996</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-71.54897</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1245,37 +1245,37 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>113455</t>
+          <t>277673</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JOHN G. LAKE</t>
+          <t>MI PEQUEÑO ESPACIO</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-16.33252</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-71.54936</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>-16.3918</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-71.54784</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>825959</t>
+          <t>113455</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JOULE CAYMA</t>
+          <t>JOHN G. LAKE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-16.3593</t>
+          <t>485</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-71.5414</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>-16.33252</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-71.54936</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>59298</t>
+          <t>059811</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MARIA MAZZARELLO</t>
+          <t>EL NAZARENO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-16.33065</t>
+          <t>351</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-71.5448</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>-16.326817</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-71.549977</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>547873</t>
+          <t>059806</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SAN JUAN MASIAS</t>
+          <t>CRISTO REY</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-16.331039</t>
+          <t>630</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-71.549037</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>-16.3259</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-71.5487</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>58963</t>
+          <t>059298</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>EL PIONERO G-2</t>
+          <t>MARIA MAZZARELLO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-16.3364</t>
+          <t>344</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-71.5532</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>-16.33065</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-71.5448</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>747754</t>
+          <t>059284</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>REY DE REYES</t>
+          <t>JAMES CLERK MAXWELL</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-16.386375</t>
+          <t>1126</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-71.5499</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>-16.3659</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-71.54599</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>59175</t>
+          <t>059175</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1627,22 +1627,22 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
           <t>-16.355156</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>-71.542939</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>363</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,37 +1679,37 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>58760</t>
+          <t>059118</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>40669 DEAN VALDIVIA</t>
+          <t>FLORA TRISTAN</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-16.32934</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-71.544851</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>-16.391</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-71.54756</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>779636</t>
+          <t>059019</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>REY DE REYES</t>
+          <t>SAN JOSE DE CALASANZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-16.38469</t>
+          <t>413</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-71.5503</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>-16.33053</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-71.545966</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>59806</t>
+          <t>058977</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CRISTO REY</t>
+          <t>LEON XIII</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-16.3259</t>
+          <t>909</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-71.5487</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>-16.34986</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-71.54288</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>58623</t>
+          <t>058963</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>40040 JOSE TRINIDAD MORAN</t>
+          <t>EL PIONERO G-2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-16.34449</t>
+          <t>372</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-71.54299</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>-16.3364</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-71.5532</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>546345</t>
+          <t>058859</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>EL MERCEDARIO RVDO PADRE ELEUTERIO ALARCON BEJARANO</t>
+          <t>HONORIO DELGADO ESPINOZA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-16.34483</t>
+          <t>1203</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-71.54368</t>
+          <t>68</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>-16.3874</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-71.5489</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>58642</t>
+          <t>058760</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>40046 JOSE L. CORNEJO A.</t>
+          <t>40669 DEAN VALDIVIA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-16.36185</t>
+          <t>606</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-71.5422</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>-16.32934</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-71.544851</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>58699</t>
+          <t>058755</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>40052 EL PERUANO DEL MILENIO ALMIRANTE MIGUEL GRAU</t>
+          <t>40654</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-16.35301</t>
+          <t>268</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-71.55</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>-16.33843</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-71.54356</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>547613</t>
+          <t>058741</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>40616 CASIMIRO CUADROS I</t>
+          <t>40618 MONSEÑOR JOSE DE PIRO D' AMICO INGUANEZ / 40618 MONSEÑOR JOSE DE PIRO D'AMICO INGUANEZ</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-16.34831</t>
+          <t>286</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-71.55227</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>-16.362225</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>-71.5453</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,37 +2175,37 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>58656</t>
+          <t>058717</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>40049 CORONEL FRANCISCO BOLOGNESI CERVANTES</t>
+          <t>40606 SEUL</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-16.35085</t>
+          <t>260</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-71.54295</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>-16.34906</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-71.54868</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>59284</t>
+          <t>058699</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>JAMES CLERK MAXWELL</t>
+          <t>40052 EL PERUANO DEL MILENIO ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-16.3659</t>
+          <t>635</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-71.54599</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1126</t>
+          <t>-16.35301</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>-71.55</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>58977</t>
+          <t>058656</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>LEON XIII</t>
+          <t>40049 CORONEL FRANCISCO BOLOGNESI CERVANTES</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-16.34986</t>
+          <t>896</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-71.54288</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>-16.35085</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>-71.54295</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>851298</t>
+          <t>058642</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO DE ASIS</t>
+          <t>40046 JOSE L. CORNEJO A.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-16.38125</t>
+          <t>547</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-71.539879</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>-16.36185</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>-71.5422</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>58859</t>
+          <t>058623</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>HONORIO DELGADO ESPINOZA</t>
+          <t>40040 JOSE TRINIDAD MORAN</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-16.3874</t>
+          <t>453</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-71.5489</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>-16.34449</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>-71.54299</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">

--- a/ZonasEscolares/excels/AREQUIPA-AREQUIPA-CAYMA.xlsx
+++ b/ZonasEscolares/excels/AREQUIPA-AREQUIPA-CAYMA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
